--- a/public/plantilla-registro-personal.xlsx
+++ b/public/plantilla-registro-personal.xlsx
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="41">
+  <numFmts count="0"/>
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -305,6 +306,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1033,7 +1038,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="366">
+  <cellXfs count="375">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1955,6 +1960,37 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2701,12 +2737,12 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="89" t="n"/>
+      <c r="C11" s="366" t="n"/>
+      <c r="D11" s="367" t="n"/>
+      <c r="E11" s="367" t="n"/>
+      <c r="F11" s="367" t="n"/>
+      <c r="G11" s="367" t="n"/>
+      <c r="H11" s="368" t="n"/>
       <c r="I11" s="59" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
@@ -2714,9 +2750,9 @@
       </c>
       <c r="J11" s="93" t="n"/>
       <c r="K11" s="89" t="n"/>
-      <c r="L11" s="69" t="n"/>
-      <c r="M11" s="93" t="n"/>
-      <c r="N11" s="89" t="n"/>
+      <c r="L11" s="369" t="n"/>
+      <c r="M11" s="367" t="n"/>
+      <c r="N11" s="368" t="n"/>
     </row>
     <row r="12" ht="19" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2725,12 +2761,12 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="93" t="n"/>
-      <c r="H12" s="89" t="n"/>
+      <c r="C12" s="366" t="n"/>
+      <c r="D12" s="367" t="n"/>
+      <c r="E12" s="367" t="n"/>
+      <c r="F12" s="367" t="n"/>
+      <c r="G12" s="367" t="n"/>
+      <c r="H12" s="368" t="n"/>
       <c r="I12" s="59" t="inlineStr">
         <is>
           <t>Hoja N°</t>
@@ -2738,9 +2774,9 @@
       </c>
       <c r="J12" s="93" t="n"/>
       <c r="K12" s="89" t="n"/>
-      <c r="L12" s="69" t="n"/>
-      <c r="M12" s="93" t="n"/>
-      <c r="N12" s="89" t="n"/>
+      <c r="L12" s="369" t="n"/>
+      <c r="M12" s="367" t="n"/>
+      <c r="N12" s="368" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="127">
       <c r="A13" s="137" t="inlineStr">
@@ -2835,400 +2871,400 @@
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" s="127">
-      <c r="A15" s="306" t="n">
+      <c r="A15" s="370" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="230" t="n"/>
-      <c r="C15" s="306" t="n"/>
-      <c r="D15" s="230" t="n"/>
-      <c r="E15" s="230" t="n"/>
-      <c r="F15" s="306" t="n"/>
-      <c r="G15" s="230" t="n"/>
-      <c r="H15" s="230" t="n"/>
-      <c r="I15" s="306" t="n"/>
-      <c r="J15" s="306" t="n"/>
-      <c r="K15" s="306" t="n"/>
-      <c r="L15" s="306" t="n"/>
-      <c r="M15" s="306" t="n"/>
-      <c r="N15" s="230" t="n"/>
+      <c r="B15" s="371" t="n"/>
+      <c r="C15" s="372" t="n"/>
+      <c r="D15" s="371" t="n"/>
+      <c r="E15" s="371" t="n"/>
+      <c r="F15" s="372" t="n"/>
+      <c r="G15" s="371" t="n"/>
+      <c r="H15" s="371" t="n"/>
+      <c r="I15" s="372" t="n"/>
+      <c r="J15" s="372" t="n"/>
+      <c r="K15" s="372" t="n"/>
+      <c r="L15" s="372" t="n"/>
+      <c r="M15" s="372" t="n"/>
+      <c r="N15" s="371" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1" s="127">
-      <c r="A16" s="306" t="n">
+      <c r="A16" s="370" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="230" t="n"/>
-      <c r="C16" s="306" t="n"/>
-      <c r="D16" s="230" t="n"/>
-      <c r="E16" s="230" t="n"/>
-      <c r="F16" s="306" t="n"/>
-      <c r="G16" s="230" t="n"/>
-      <c r="H16" s="230" t="n"/>
-      <c r="I16" s="306" t="n"/>
-      <c r="J16" s="306" t="n"/>
-      <c r="K16" s="306" t="n"/>
-      <c r="L16" s="306" t="n"/>
-      <c r="M16" s="306" t="n"/>
-      <c r="N16" s="230" t="n"/>
+      <c r="B16" s="371" t="n"/>
+      <c r="C16" s="372" t="n"/>
+      <c r="D16" s="371" t="n"/>
+      <c r="E16" s="371" t="n"/>
+      <c r="F16" s="372" t="n"/>
+      <c r="G16" s="371" t="n"/>
+      <c r="H16" s="371" t="n"/>
+      <c r="I16" s="372" t="n"/>
+      <c r="J16" s="372" t="n"/>
+      <c r="K16" s="372" t="n"/>
+      <c r="L16" s="372" t="n"/>
+      <c r="M16" s="372" t="n"/>
+      <c r="N16" s="371" t="n"/>
     </row>
     <row r="17" ht="19" customHeight="1" s="127">
-      <c r="A17" s="306" t="n">
+      <c r="A17" s="370" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="230" t="n"/>
-      <c r="C17" s="306" t="n"/>
-      <c r="D17" s="230" t="n"/>
-      <c r="E17" s="230" t="n"/>
-      <c r="F17" s="306" t="n"/>
-      <c r="G17" s="230" t="n"/>
-      <c r="H17" s="230" t="n"/>
-      <c r="I17" s="306" t="n"/>
-      <c r="J17" s="306" t="n"/>
-      <c r="K17" s="306" t="n"/>
-      <c r="L17" s="306" t="n"/>
-      <c r="M17" s="306" t="n"/>
-      <c r="N17" s="230" t="n"/>
+      <c r="B17" s="371" t="n"/>
+      <c r="C17" s="372" t="n"/>
+      <c r="D17" s="371" t="n"/>
+      <c r="E17" s="371" t="n"/>
+      <c r="F17" s="372" t="n"/>
+      <c r="G17" s="371" t="n"/>
+      <c r="H17" s="371" t="n"/>
+      <c r="I17" s="372" t="n"/>
+      <c r="J17" s="372" t="n"/>
+      <c r="K17" s="372" t="n"/>
+      <c r="L17" s="372" t="n"/>
+      <c r="M17" s="372" t="n"/>
+      <c r="N17" s="371" t="n"/>
     </row>
     <row r="18" ht="19" customHeight="1" s="127">
-      <c r="A18" s="306" t="n">
+      <c r="A18" s="370" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="230" t="n"/>
-      <c r="C18" s="306" t="n"/>
-      <c r="D18" s="230" t="n"/>
-      <c r="E18" s="230" t="n"/>
-      <c r="F18" s="306" t="n"/>
-      <c r="G18" s="230" t="n"/>
-      <c r="H18" s="230" t="n"/>
-      <c r="I18" s="306" t="n"/>
-      <c r="J18" s="306" t="n"/>
-      <c r="K18" s="306" t="n"/>
-      <c r="L18" s="306" t="n"/>
-      <c r="M18" s="306" t="n"/>
-      <c r="N18" s="230" t="n"/>
+      <c r="B18" s="371" t="n"/>
+      <c r="C18" s="372" t="n"/>
+      <c r="D18" s="371" t="n"/>
+      <c r="E18" s="371" t="n"/>
+      <c r="F18" s="372" t="n"/>
+      <c r="G18" s="371" t="n"/>
+      <c r="H18" s="371" t="n"/>
+      <c r="I18" s="372" t="n"/>
+      <c r="J18" s="372" t="n"/>
+      <c r="K18" s="372" t="n"/>
+      <c r="L18" s="372" t="n"/>
+      <c r="M18" s="372" t="n"/>
+      <c r="N18" s="371" t="n"/>
     </row>
     <row r="19" ht="19" customHeight="1" s="127">
-      <c r="A19" s="306" t="n">
+      <c r="A19" s="370" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="230" t="n"/>
-      <c r="C19" s="306" t="n"/>
-      <c r="D19" s="230" t="n"/>
-      <c r="E19" s="230" t="n"/>
-      <c r="F19" s="306" t="n"/>
-      <c r="G19" s="230" t="n"/>
-      <c r="H19" s="230" t="n"/>
-      <c r="I19" s="306" t="n"/>
-      <c r="J19" s="306" t="n"/>
-      <c r="K19" s="306" t="n"/>
-      <c r="L19" s="306" t="n"/>
-      <c r="M19" s="306" t="n"/>
-      <c r="N19" s="230" t="n"/>
+      <c r="B19" s="371" t="n"/>
+      <c r="C19" s="372" t="n"/>
+      <c r="D19" s="371" t="n"/>
+      <c r="E19" s="371" t="n"/>
+      <c r="F19" s="372" t="n"/>
+      <c r="G19" s="371" t="n"/>
+      <c r="H19" s="371" t="n"/>
+      <c r="I19" s="372" t="n"/>
+      <c r="J19" s="372" t="n"/>
+      <c r="K19" s="372" t="n"/>
+      <c r="L19" s="372" t="n"/>
+      <c r="M19" s="372" t="n"/>
+      <c r="N19" s="371" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1" s="127">
-      <c r="A20" s="306" t="n">
+      <c r="A20" s="370" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="230" t="n"/>
-      <c r="C20" s="306" t="n"/>
-      <c r="D20" s="230" t="n"/>
-      <c r="E20" s="230" t="n"/>
-      <c r="F20" s="306" t="n"/>
-      <c r="G20" s="230" t="n"/>
-      <c r="H20" s="230" t="n"/>
-      <c r="I20" s="306" t="n"/>
-      <c r="J20" s="306" t="n"/>
-      <c r="K20" s="306" t="n"/>
-      <c r="L20" s="306" t="n"/>
-      <c r="M20" s="306" t="n"/>
-      <c r="N20" s="230" t="n"/>
+      <c r="B20" s="371" t="n"/>
+      <c r="C20" s="372" t="n"/>
+      <c r="D20" s="371" t="n"/>
+      <c r="E20" s="371" t="n"/>
+      <c r="F20" s="372" t="n"/>
+      <c r="G20" s="371" t="n"/>
+      <c r="H20" s="371" t="n"/>
+      <c r="I20" s="372" t="n"/>
+      <c r="J20" s="372" t="n"/>
+      <c r="K20" s="372" t="n"/>
+      <c r="L20" s="372" t="n"/>
+      <c r="M20" s="372" t="n"/>
+      <c r="N20" s="371" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1" s="127">
-      <c r="A21" s="306" t="n">
+      <c r="A21" s="370" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="230" t="n"/>
-      <c r="C21" s="306" t="n"/>
-      <c r="D21" s="230" t="n"/>
-      <c r="E21" s="230" t="n"/>
-      <c r="F21" s="306" t="n"/>
-      <c r="G21" s="230" t="n"/>
-      <c r="H21" s="230" t="n"/>
-      <c r="I21" s="306" t="n"/>
-      <c r="J21" s="306" t="n"/>
-      <c r="K21" s="306" t="n"/>
-      <c r="L21" s="306" t="n"/>
-      <c r="M21" s="306" t="n"/>
-      <c r="N21" s="230" t="n"/>
+      <c r="B21" s="371" t="n"/>
+      <c r="C21" s="372" t="n"/>
+      <c r="D21" s="371" t="n"/>
+      <c r="E21" s="371" t="n"/>
+      <c r="F21" s="372" t="n"/>
+      <c r="G21" s="371" t="n"/>
+      <c r="H21" s="371" t="n"/>
+      <c r="I21" s="372" t="n"/>
+      <c r="J21" s="372" t="n"/>
+      <c r="K21" s="372" t="n"/>
+      <c r="L21" s="372" t="n"/>
+      <c r="M21" s="372" t="n"/>
+      <c r="N21" s="371" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1" s="127">
-      <c r="A22" s="306" t="n">
+      <c r="A22" s="370" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="230" t="n"/>
-      <c r="C22" s="306" t="n"/>
-      <c r="D22" s="230" t="n"/>
-      <c r="E22" s="230" t="n"/>
-      <c r="F22" s="306" t="n"/>
-      <c r="G22" s="230" t="n"/>
-      <c r="H22" s="230" t="n"/>
-      <c r="I22" s="306" t="n"/>
-      <c r="J22" s="306" t="n"/>
-      <c r="K22" s="306" t="n"/>
-      <c r="L22" s="306" t="n"/>
-      <c r="M22" s="306" t="n"/>
-      <c r="N22" s="230" t="n"/>
+      <c r="B22" s="371" t="n"/>
+      <c r="C22" s="372" t="n"/>
+      <c r="D22" s="371" t="n"/>
+      <c r="E22" s="371" t="n"/>
+      <c r="F22" s="372" t="n"/>
+      <c r="G22" s="371" t="n"/>
+      <c r="H22" s="371" t="n"/>
+      <c r="I22" s="372" t="n"/>
+      <c r="J22" s="372" t="n"/>
+      <c r="K22" s="372" t="n"/>
+      <c r="L22" s="372" t="n"/>
+      <c r="M22" s="372" t="n"/>
+      <c r="N22" s="371" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1" s="127">
-      <c r="A23" s="306" t="n">
+      <c r="A23" s="370" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="230" t="n"/>
-      <c r="C23" s="306" t="n"/>
-      <c r="D23" s="230" t="n"/>
-      <c r="E23" s="230" t="n"/>
-      <c r="F23" s="306" t="n"/>
-      <c r="G23" s="230" t="n"/>
-      <c r="H23" s="230" t="n"/>
-      <c r="I23" s="306" t="n"/>
-      <c r="J23" s="306" t="n"/>
-      <c r="K23" s="306" t="n"/>
-      <c r="L23" s="306" t="n"/>
-      <c r="M23" s="306" t="n"/>
-      <c r="N23" s="230" t="n"/>
+      <c r="B23" s="371" t="n"/>
+      <c r="C23" s="372" t="n"/>
+      <c r="D23" s="371" t="n"/>
+      <c r="E23" s="371" t="n"/>
+      <c r="F23" s="372" t="n"/>
+      <c r="G23" s="371" t="n"/>
+      <c r="H23" s="371" t="n"/>
+      <c r="I23" s="372" t="n"/>
+      <c r="J23" s="372" t="n"/>
+      <c r="K23" s="372" t="n"/>
+      <c r="L23" s="372" t="n"/>
+      <c r="M23" s="372" t="n"/>
+      <c r="N23" s="371" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1" s="127">
-      <c r="A24" s="306" t="n">
+      <c r="A24" s="370" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="230" t="n"/>
-      <c r="C24" s="306" t="n"/>
-      <c r="D24" s="230" t="n"/>
-      <c r="E24" s="230" t="n"/>
-      <c r="F24" s="306" t="n"/>
-      <c r="G24" s="230" t="n"/>
-      <c r="H24" s="230" t="n"/>
-      <c r="I24" s="306" t="n"/>
-      <c r="J24" s="306" t="n"/>
-      <c r="K24" s="306" t="n"/>
-      <c r="L24" s="306" t="n"/>
-      <c r="M24" s="306" t="n"/>
-      <c r="N24" s="230" t="n"/>
+      <c r="B24" s="371" t="n"/>
+      <c r="C24" s="372" t="n"/>
+      <c r="D24" s="371" t="n"/>
+      <c r="E24" s="371" t="n"/>
+      <c r="F24" s="372" t="n"/>
+      <c r="G24" s="371" t="n"/>
+      <c r="H24" s="371" t="n"/>
+      <c r="I24" s="372" t="n"/>
+      <c r="J24" s="372" t="n"/>
+      <c r="K24" s="372" t="n"/>
+      <c r="L24" s="372" t="n"/>
+      <c r="M24" s="372" t="n"/>
+      <c r="N24" s="371" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1" s="127">
-      <c r="A25" s="306" t="n">
+      <c r="A25" s="370" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="230" t="n"/>
-      <c r="C25" s="306" t="n"/>
-      <c r="D25" s="230" t="n"/>
-      <c r="E25" s="230" t="n"/>
-      <c r="F25" s="306" t="n"/>
-      <c r="G25" s="230" t="n"/>
-      <c r="H25" s="230" t="n"/>
-      <c r="I25" s="306" t="n"/>
-      <c r="J25" s="306" t="n"/>
-      <c r="K25" s="306" t="n"/>
-      <c r="L25" s="306" t="n"/>
-      <c r="M25" s="306" t="n"/>
-      <c r="N25" s="230" t="n"/>
+      <c r="B25" s="371" t="n"/>
+      <c r="C25" s="372" t="n"/>
+      <c r="D25" s="371" t="n"/>
+      <c r="E25" s="371" t="n"/>
+      <c r="F25" s="372" t="n"/>
+      <c r="G25" s="371" t="n"/>
+      <c r="H25" s="371" t="n"/>
+      <c r="I25" s="372" t="n"/>
+      <c r="J25" s="372" t="n"/>
+      <c r="K25" s="372" t="n"/>
+      <c r="L25" s="372" t="n"/>
+      <c r="M25" s="372" t="n"/>
+      <c r="N25" s="371" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1" s="127">
-      <c r="A26" s="306" t="n">
+      <c r="A26" s="370" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="230" t="n"/>
-      <c r="C26" s="306" t="n"/>
-      <c r="D26" s="230" t="n"/>
-      <c r="E26" s="230" t="n"/>
-      <c r="F26" s="306" t="n"/>
-      <c r="G26" s="230" t="n"/>
-      <c r="H26" s="230" t="n"/>
-      <c r="I26" s="306" t="n"/>
-      <c r="J26" s="306" t="n"/>
-      <c r="K26" s="306" t="n"/>
-      <c r="L26" s="306" t="n"/>
-      <c r="M26" s="306" t="n"/>
-      <c r="N26" s="230" t="n"/>
+      <c r="B26" s="371" t="n"/>
+      <c r="C26" s="372" t="n"/>
+      <c r="D26" s="371" t="n"/>
+      <c r="E26" s="371" t="n"/>
+      <c r="F26" s="372" t="n"/>
+      <c r="G26" s="371" t="n"/>
+      <c r="H26" s="371" t="n"/>
+      <c r="I26" s="372" t="n"/>
+      <c r="J26" s="372" t="n"/>
+      <c r="K26" s="372" t="n"/>
+      <c r="L26" s="372" t="n"/>
+      <c r="M26" s="372" t="n"/>
+      <c r="N26" s="371" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1" s="127">
-      <c r="A27" s="306" t="n">
+      <c r="A27" s="370" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="230" t="n"/>
-      <c r="C27" s="306" t="n"/>
-      <c r="D27" s="230" t="n"/>
-      <c r="E27" s="230" t="n"/>
-      <c r="F27" s="306" t="n"/>
-      <c r="G27" s="230" t="n"/>
-      <c r="H27" s="230" t="n"/>
-      <c r="I27" s="306" t="n"/>
-      <c r="J27" s="306" t="n"/>
-      <c r="K27" s="306" t="n"/>
-      <c r="L27" s="306" t="n"/>
-      <c r="M27" s="306" t="n"/>
-      <c r="N27" s="230" t="n"/>
+      <c r="B27" s="371" t="n"/>
+      <c r="C27" s="372" t="n"/>
+      <c r="D27" s="371" t="n"/>
+      <c r="E27" s="371" t="n"/>
+      <c r="F27" s="372" t="n"/>
+      <c r="G27" s="371" t="n"/>
+      <c r="H27" s="371" t="n"/>
+      <c r="I27" s="372" t="n"/>
+      <c r="J27" s="372" t="n"/>
+      <c r="K27" s="372" t="n"/>
+      <c r="L27" s="372" t="n"/>
+      <c r="M27" s="372" t="n"/>
+      <c r="N27" s="371" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1" s="127">
-      <c r="A28" s="306" t="n">
+      <c r="A28" s="370" t="n">
         <v>14</v>
       </c>
-      <c r="B28" s="230" t="n"/>
-      <c r="C28" s="306" t="n"/>
-      <c r="D28" s="230" t="n"/>
-      <c r="E28" s="230" t="n"/>
-      <c r="F28" s="306" t="n"/>
-      <c r="G28" s="230" t="n"/>
-      <c r="H28" s="230" t="n"/>
-      <c r="I28" s="306" t="n"/>
-      <c r="J28" s="306" t="n"/>
-      <c r="K28" s="306" t="n"/>
-      <c r="L28" s="306" t="n"/>
-      <c r="M28" s="306" t="n"/>
-      <c r="N28" s="230" t="n"/>
+      <c r="B28" s="371" t="n"/>
+      <c r="C28" s="372" t="n"/>
+      <c r="D28" s="371" t="n"/>
+      <c r="E28" s="371" t="n"/>
+      <c r="F28" s="372" t="n"/>
+      <c r="G28" s="371" t="n"/>
+      <c r="H28" s="371" t="n"/>
+      <c r="I28" s="372" t="n"/>
+      <c r="J28" s="372" t="n"/>
+      <c r="K28" s="372" t="n"/>
+      <c r="L28" s="372" t="n"/>
+      <c r="M28" s="372" t="n"/>
+      <c r="N28" s="371" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1" s="127">
-      <c r="A29" s="306" t="n">
+      <c r="A29" s="370" t="n">
         <v>15</v>
       </c>
-      <c r="B29" s="230" t="n"/>
-      <c r="C29" s="306" t="n"/>
-      <c r="D29" s="230" t="n"/>
-      <c r="E29" s="230" t="n"/>
-      <c r="F29" s="306" t="n"/>
-      <c r="G29" s="230" t="n"/>
-      <c r="H29" s="230" t="n"/>
-      <c r="I29" s="306" t="n"/>
-      <c r="J29" s="306" t="n"/>
-      <c r="K29" s="306" t="n"/>
-      <c r="L29" s="306" t="n"/>
-      <c r="M29" s="306" t="n"/>
-      <c r="N29" s="230" t="n"/>
+      <c r="B29" s="371" t="n"/>
+      <c r="C29" s="372" t="n"/>
+      <c r="D29" s="371" t="n"/>
+      <c r="E29" s="371" t="n"/>
+      <c r="F29" s="372" t="n"/>
+      <c r="G29" s="371" t="n"/>
+      <c r="H29" s="371" t="n"/>
+      <c r="I29" s="372" t="n"/>
+      <c r="J29" s="372" t="n"/>
+      <c r="K29" s="372" t="n"/>
+      <c r="L29" s="372" t="n"/>
+      <c r="M29" s="372" t="n"/>
+      <c r="N29" s="371" t="n"/>
     </row>
     <row r="30" ht="19" customHeight="1" s="127">
-      <c r="A30" s="306" t="n">
+      <c r="A30" s="370" t="n">
         <v>16</v>
       </c>
-      <c r="B30" s="230" t="n"/>
-      <c r="C30" s="306" t="n"/>
-      <c r="D30" s="230" t="n"/>
-      <c r="E30" s="230" t="n"/>
-      <c r="F30" s="306" t="n"/>
-      <c r="G30" s="230" t="n"/>
-      <c r="H30" s="230" t="n"/>
-      <c r="I30" s="306" t="n"/>
-      <c r="J30" s="306" t="n"/>
-      <c r="K30" s="306" t="n"/>
-      <c r="L30" s="306" t="n"/>
-      <c r="M30" s="306" t="n"/>
-      <c r="N30" s="230" t="n"/>
+      <c r="B30" s="371" t="n"/>
+      <c r="C30" s="372" t="n"/>
+      <c r="D30" s="371" t="n"/>
+      <c r="E30" s="371" t="n"/>
+      <c r="F30" s="372" t="n"/>
+      <c r="G30" s="371" t="n"/>
+      <c r="H30" s="371" t="n"/>
+      <c r="I30" s="372" t="n"/>
+      <c r="J30" s="372" t="n"/>
+      <c r="K30" s="372" t="n"/>
+      <c r="L30" s="372" t="n"/>
+      <c r="M30" s="372" t="n"/>
+      <c r="N30" s="371" t="n"/>
     </row>
     <row r="31" ht="19" customHeight="1" s="127">
-      <c r="A31" s="306" t="n">
+      <c r="A31" s="370" t="n">
         <v>17</v>
       </c>
-      <c r="B31" s="230" t="n"/>
-      <c r="C31" s="306" t="n"/>
-      <c r="D31" s="230" t="n"/>
-      <c r="E31" s="230" t="n"/>
-      <c r="F31" s="306" t="n"/>
-      <c r="G31" s="230" t="n"/>
-      <c r="H31" s="230" t="n"/>
-      <c r="I31" s="306" t="n"/>
-      <c r="J31" s="306" t="n"/>
-      <c r="K31" s="306" t="n"/>
-      <c r="L31" s="306" t="n"/>
-      <c r="M31" s="306" t="n"/>
-      <c r="N31" s="230" t="n"/>
+      <c r="B31" s="371" t="n"/>
+      <c r="C31" s="372" t="n"/>
+      <c r="D31" s="371" t="n"/>
+      <c r="E31" s="371" t="n"/>
+      <c r="F31" s="372" t="n"/>
+      <c r="G31" s="371" t="n"/>
+      <c r="H31" s="371" t="n"/>
+      <c r="I31" s="372" t="n"/>
+      <c r="J31" s="372" t="n"/>
+      <c r="K31" s="372" t="n"/>
+      <c r="L31" s="372" t="n"/>
+      <c r="M31" s="372" t="n"/>
+      <c r="N31" s="371" t="n"/>
     </row>
     <row r="32" ht="19" customHeight="1" s="127">
-      <c r="A32" s="306" t="n">
+      <c r="A32" s="370" t="n">
         <v>18</v>
       </c>
-      <c r="B32" s="230" t="n"/>
-      <c r="C32" s="306" t="n"/>
-      <c r="D32" s="230" t="n"/>
-      <c r="E32" s="230" t="n"/>
-      <c r="F32" s="306" t="n"/>
-      <c r="G32" s="230" t="n"/>
-      <c r="H32" s="230" t="n"/>
-      <c r="I32" s="306" t="n"/>
-      <c r="J32" s="306" t="n"/>
-      <c r="K32" s="306" t="n"/>
-      <c r="L32" s="306" t="n"/>
-      <c r="M32" s="306" t="n"/>
-      <c r="N32" s="230" t="n"/>
+      <c r="B32" s="371" t="n"/>
+      <c r="C32" s="372" t="n"/>
+      <c r="D32" s="371" t="n"/>
+      <c r="E32" s="371" t="n"/>
+      <c r="F32" s="372" t="n"/>
+      <c r="G32" s="371" t="n"/>
+      <c r="H32" s="371" t="n"/>
+      <c r="I32" s="372" t="n"/>
+      <c r="J32" s="372" t="n"/>
+      <c r="K32" s="372" t="n"/>
+      <c r="L32" s="372" t="n"/>
+      <c r="M32" s="372" t="n"/>
+      <c r="N32" s="371" t="n"/>
     </row>
     <row r="33" ht="19" customHeight="1" s="127">
-      <c r="A33" s="306" t="n">
+      <c r="A33" s="370" t="n">
         <v>19</v>
       </c>
-      <c r="B33" s="230" t="n"/>
-      <c r="C33" s="306" t="n"/>
-      <c r="D33" s="230" t="n"/>
-      <c r="E33" s="230" t="n"/>
-      <c r="F33" s="306" t="n"/>
-      <c r="G33" s="230" t="n"/>
-      <c r="H33" s="230" t="n"/>
-      <c r="I33" s="306" t="n"/>
-      <c r="J33" s="306" t="n"/>
-      <c r="K33" s="306" t="n"/>
-      <c r="L33" s="306" t="n"/>
-      <c r="M33" s="306" t="n"/>
-      <c r="N33" s="230" t="n"/>
+      <c r="B33" s="371" t="n"/>
+      <c r="C33" s="372" t="n"/>
+      <c r="D33" s="371" t="n"/>
+      <c r="E33" s="371" t="n"/>
+      <c r="F33" s="372" t="n"/>
+      <c r="G33" s="371" t="n"/>
+      <c r="H33" s="371" t="n"/>
+      <c r="I33" s="372" t="n"/>
+      <c r="J33" s="372" t="n"/>
+      <c r="K33" s="372" t="n"/>
+      <c r="L33" s="372" t="n"/>
+      <c r="M33" s="372" t="n"/>
+      <c r="N33" s="371" t="n"/>
     </row>
     <row r="34" ht="19" customHeight="1" s="127">
-      <c r="A34" s="306" t="n">
+      <c r="A34" s="370" t="n">
         <v>20</v>
       </c>
-      <c r="B34" s="230" t="n"/>
-      <c r="C34" s="306" t="n"/>
-      <c r="D34" s="230" t="n"/>
-      <c r="E34" s="230" t="n"/>
-      <c r="F34" s="306" t="n"/>
-      <c r="G34" s="230" t="n"/>
-      <c r="H34" s="230" t="n"/>
-      <c r="I34" s="306" t="n"/>
-      <c r="J34" s="306" t="n"/>
-      <c r="K34" s="306" t="n"/>
-      <c r="L34" s="306" t="n"/>
-      <c r="M34" s="306" t="n"/>
-      <c r="N34" s="230" t="n"/>
+      <c r="B34" s="371" t="n"/>
+      <c r="C34" s="372" t="n"/>
+      <c r="D34" s="371" t="n"/>
+      <c r="E34" s="371" t="n"/>
+      <c r="F34" s="372" t="n"/>
+      <c r="G34" s="371" t="n"/>
+      <c r="H34" s="371" t="n"/>
+      <c r="I34" s="372" t="n"/>
+      <c r="J34" s="372" t="n"/>
+      <c r="K34" s="372" t="n"/>
+      <c r="L34" s="372" t="n"/>
+      <c r="M34" s="372" t="n"/>
+      <c r="N34" s="371" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1" s="127">
-      <c r="A35" s="306" t="n">
+      <c r="A35" s="370" t="n">
         <v>21</v>
       </c>
-      <c r="B35" s="230" t="n"/>
-      <c r="C35" s="306" t="n"/>
-      <c r="D35" s="230" t="n"/>
-      <c r="E35" s="230" t="n"/>
-      <c r="F35" s="306" t="n"/>
-      <c r="G35" s="230" t="n"/>
-      <c r="H35" s="230" t="n"/>
-      <c r="I35" s="306" t="n"/>
-      <c r="J35" s="306" t="n"/>
-      <c r="K35" s="306" t="n"/>
-      <c r="L35" s="306" t="n"/>
-      <c r="M35" s="306" t="n"/>
-      <c r="N35" s="230" t="n"/>
+      <c r="B35" s="371" t="n"/>
+      <c r="C35" s="372" t="n"/>
+      <c r="D35" s="371" t="n"/>
+      <c r="E35" s="371" t="n"/>
+      <c r="F35" s="372" t="n"/>
+      <c r="G35" s="371" t="n"/>
+      <c r="H35" s="371" t="n"/>
+      <c r="I35" s="372" t="n"/>
+      <c r="J35" s="372" t="n"/>
+      <c r="K35" s="372" t="n"/>
+      <c r="L35" s="372" t="n"/>
+      <c r="M35" s="372" t="n"/>
+      <c r="N35" s="371" t="n"/>
     </row>
     <row r="36" ht="19" customHeight="1" s="127">
-      <c r="A36" s="306" t="n">
+      <c r="A36" s="370" t="n">
         <v>22</v>
       </c>
-      <c r="B36" s="230" t="n"/>
-      <c r="C36" s="306" t="n"/>
-      <c r="D36" s="230" t="n"/>
-      <c r="E36" s="230" t="n"/>
-      <c r="F36" s="306" t="n"/>
-      <c r="G36" s="230" t="n"/>
-      <c r="H36" s="230" t="n"/>
-      <c r="I36" s="306" t="n"/>
-      <c r="J36" s="306" t="n"/>
-      <c r="K36" s="306" t="n"/>
-      <c r="L36" s="306" t="n"/>
-      <c r="M36" s="306" t="n"/>
-      <c r="N36" s="230" t="n"/>
+      <c r="B36" s="371" t="n"/>
+      <c r="C36" s="372" t="n"/>
+      <c r="D36" s="371" t="n"/>
+      <c r="E36" s="371" t="n"/>
+      <c r="F36" s="372" t="n"/>
+      <c r="G36" s="371" t="n"/>
+      <c r="H36" s="371" t="n"/>
+      <c r="I36" s="372" t="n"/>
+      <c r="J36" s="372" t="n"/>
+      <c r="K36" s="372" t="n"/>
+      <c r="L36" s="372" t="n"/>
+      <c r="M36" s="372" t="n"/>
+      <c r="N36" s="371" t="n"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="127">
       <c r="A37" s="137" t="inlineStr">
@@ -3406,26 +3442,26 @@
         </is>
       </c>
       <c r="B43" s="97" t="n"/>
-      <c r="C43" s="301" t="n"/>
-      <c r="D43" s="98" t="n"/>
-      <c r="E43" s="97" t="n"/>
+      <c r="C43" s="371" t="n"/>
+      <c r="D43" s="373" t="n"/>
+      <c r="E43" s="374" t="n"/>
       <c r="F43" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="G43" s="97" t="n"/>
-      <c r="H43" s="301" t="n"/>
-      <c r="I43" s="98" t="n"/>
-      <c r="J43" s="97" t="n"/>
+      <c r="H43" s="371" t="n"/>
+      <c r="I43" s="373" t="n"/>
+      <c r="J43" s="374" t="n"/>
       <c r="K43" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="L43" s="97" t="n"/>
-      <c r="M43" s="301" t="n"/>
-      <c r="N43" s="97" t="n"/>
+      <c r="M43" s="371" t="n"/>
+      <c r="N43" s="374" t="n"/>
     </row>
     <row r="44" ht="21" customHeight="1" s="127">
       <c r="A44" s="302" t="inlineStr">
@@ -3434,26 +3470,26 @@
         </is>
       </c>
       <c r="B44" s="97" t="n"/>
-      <c r="C44" s="301" t="n"/>
-      <c r="D44" s="98" t="n"/>
-      <c r="E44" s="97" t="n"/>
+      <c r="C44" s="371" t="n"/>
+      <c r="D44" s="373" t="n"/>
+      <c r="E44" s="374" t="n"/>
       <c r="F44" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="G44" s="97" t="n"/>
-      <c r="H44" s="301" t="n"/>
-      <c r="I44" s="98" t="n"/>
-      <c r="J44" s="97" t="n"/>
+      <c r="H44" s="371" t="n"/>
+      <c r="I44" s="373" t="n"/>
+      <c r="J44" s="374" t="n"/>
       <c r="K44" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="L44" s="97" t="n"/>
-      <c r="M44" s="301" t="n"/>
-      <c r="N44" s="97" t="n"/>
+      <c r="M44" s="371" t="n"/>
+      <c r="N44" s="374" t="n"/>
     </row>
     <row r="45" ht="21" customHeight="1" s="127">
       <c r="A45" s="302" t="inlineStr">
@@ -3462,26 +3498,26 @@
         </is>
       </c>
       <c r="B45" s="97" t="n"/>
-      <c r="C45" s="301" t="n"/>
-      <c r="D45" s="98" t="n"/>
-      <c r="E45" s="97" t="n"/>
+      <c r="C45" s="371" t="n"/>
+      <c r="D45" s="373" t="n"/>
+      <c r="E45" s="374" t="n"/>
       <c r="F45" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="G45" s="97" t="n"/>
-      <c r="H45" s="301" t="n"/>
-      <c r="I45" s="98" t="n"/>
-      <c r="J45" s="97" t="n"/>
+      <c r="H45" s="371" t="n"/>
+      <c r="I45" s="373" t="n"/>
+      <c r="J45" s="374" t="n"/>
       <c r="K45" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="L45" s="97" t="n"/>
-      <c r="M45" s="301" t="n"/>
-      <c r="N45" s="97" t="n"/>
+      <c r="M45" s="371" t="n"/>
+      <c r="N45" s="374" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="25" t="inlineStr">
@@ -3495,6 +3531,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="57">
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="A9:N9"/>
